--- a/data/daily/2026-10/2026-10-22.xlsx
+++ b/data/daily/2026-10/2026-10-22.xlsx
@@ -1165,10 +1165,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1190,10 +1190,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1215,7 +1215,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
@@ -1240,10 +1240,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1265,7 +1265,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
@@ -1290,10 +1290,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1315,10 +1315,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1340,7 +1340,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
@@ -1365,10 +1365,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1386,31 +1386,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1418,12 +1393,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1443,12 +1418,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1468,7 +1443,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1493,12 +1468,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1518,7 +1493,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1543,12 +1518,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1568,12 +1543,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1593,7 +1568,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1618,12 +1593,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1631,31 +1606,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2088,22 +2038,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복 효과 체감 — 복용 후 컨디션 유지 및 피로 완화에 도움을 받음</t>
+          <t>피로 회복 효과 — 섭취 후 피곤함이 덜하고 컨디션 유지에 도움됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>용이한 알약 섭취 — 알약 크기가 작고 맛이 강하지 않아 잘 넘어감</t>
+          <t>편리한 복용감 — 알약 크기가 작고 맛이 무난하여 복용하기 쉬움</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>선물용 높은 만족도 — 유명한 제품으로 선물 시 만족도가 뛰어남</t>
+          <t>높은 선물 만족도 — 선물용으로 인기가 높으며 받았을 때 만족감이 큼</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>높은 가격 부담 — 제품 가격이 비싸 구매 시 부담이 큼</t>
+          <t>부담스러운 가격 — 가격대가 비싸 할인 기간을 활용하여 구매함</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2140,28 +2090,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261014103242_f88fda29ab714a8b85e0d3e6699f6e32.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261022102251_4ac3b0665f83480cbcd353f3600d626f.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15665</v>
+        <v>15667</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 액상 섭취 — 액상이 달짝지근하고 신맛이 없어 맛있게 복용 가능함</t>
+          <t>휴대성 및 깔끔 포장 — 포장이 깔끔하고 휴대하기 좋아 간편하게 챙겨 먹음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 — 복용 후 기운이 나고 피로 회복에 효과적임</t>
+          <t>달콤하고 맛있는 맛 — 액상이 달짝지근하고 시지 않아 맛있게 복용함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>안전한 뽁뽁이 포장 — 에어캡 포장으로 손상 없이 완벽하게 배송됨</t>
+          <t>기력 회복 도모 — 외출 전이나 지칠 때 기운을 차리는 데 도움됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2206,21 +2156,21 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>넉넉한 용량 구성 — 30+2입 구성으로 오래두고 챙겨 먹기 적합함</t>
+          <t>진한 액상 농도 — 타 액상 비타민 제품 대비 농도가 찐함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>진한 액상 농도 — 타 유사 액상 제품 대비 농도가 훨씬 찐함</t>
+          <t>체력 충전 효과 — 지치고 체력이 달릴 때 먹으면 힘이 남</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>실용적인 선물용 — 생일이나 건강 기원 선물로 받는 만족도가 높음</t>
+          <t>알찬 선물 구성 — 30개입으로 용량이 넉넉하여 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2269,22 +2219,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 식감 — 과일맛이 나고 적당히 말랑하며 쫄깃해 맛있음</t>
+          <t>맛있는 구미 제형 — 과일맛의 쫄깃한 젤리 형태로 간식처럼 섭취함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 씹어먹기 — 물 없이 씹어서 간 편하게 섭취 가능함</t>
+          <t>물 없는 간편 섭취 — 바쁜 아침 물 없이 씹어 먹을 수 있어 편리함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>안전 캡 포장 적용 — 안전캡이 적용되어 아이 있는 집에서도 안전함</t>
+          <t>안전캡 적용 — 안전용기가 적용되어 아이가 있는 집에서도 보관 용이함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>개봉 시 씰링 불편 — 개봉 시 비닐 포장이 잘 안 뜯겨 불편함</t>
+          <t>개봉의 어려움 — 포장이 잘 뜯기지 않아 개봉 시 다소 불편함</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2332,17 +2282,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 일상생활 피로가 잘 풀리고 컨디션 회복에 도움 됨</t>
+          <t>피로 회복 도움 — 피로 해소와 상쾌한 컨디션 유지에 효과적임</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 휴대하기 편해 외출 시 간편히 챙겨 먹기 좋음</t>
+          <t>간편한 휴대성 — 복용이 편하고 휴대하기 좋아 일상 활용도가 높음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>만족스러운 선물 구성 — 기프트 에디션 구성이 좋아 선물용으로 매우 적합함</t>
+          <t>만족스러운 패키지 — 선물용 패키지 구성과 배송 만족도가 우수함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2387,26 +2337,26 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 포장용기와 패키지가 깔끔하고 고급스러움</t>
+          <t>빠른 에너지 충전 — 달콤새콤한 맛으로 빠르게 기력이 나는 느낌임</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>상큼한 맛과 에너지 — 상큼한 맛으로 에너지가 충전되는 느낌을 받음</t>
+          <t>고급스러운 포장 — 패키지가 깔끔하고 고급스러워 응원 선물로 좋음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>빠르고 꼼꼼한 배송 — 배송이 빠르고 꼼꼼하게 포장되어 전달됨</t>
+          <t>간편한 복용법 — 깔끔하게 챙겨 먹기 유용하며 섭취가 편리함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>생소한 복용 방식 — 뚜껑을 눌러 섞어 마시는 방식이 처음엔 다소 어색함</t>
+          <t>복용 방식의 생소함 — 뚜껑을 눌러 섞어 마시는 형태라 복용법 확인이 필요함</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2454,17 +2404,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 마시는 제형 — 액상 제형으로 물 없이 간편하게 섭취 가능함</t>
+          <t>마시는 액상 제형 — 액상 형태로 섭취하기가 매우 간편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>다음 날 피로 회복 — 섭취 후 다음 날 아침 컨디션 차이를 체감함</t>
+          <t>컨디션 회복 효과 — 피곤할 때 섭취하면 기운을 차리는 데 도움됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>센스 있는 선물용 — 체력 관리가 필요한 사람에게 선물하기 좋음</t>
+          <t>빠른 배송 서비스 — 배송이 빠르고 선물용으로 주고받기 좋음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -2513,18 +2463,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>빠른 배송 및 가격 — 배송이 매우 빠르고 행사 가격으로 저렴하게 구입함</t>
+          <t>신뢰도 높은 원료 — 영국산 퀄리씨 원료를 사용하여 믿고 구매함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>믿을 수 있는 품질 — 영국산 퀄리씨 원료 사용으로 품질 신뢰도가 높음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>합리적인 가격 — 행사 및 할인가로 부담 없이 저렴하게 구매함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>메가도스에 적합 — 고용량 비타민C 메가도스 용법으로 챙기기 적합함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>매우 강한 신맛 — 정신이 번쩍 들 정도로 분말의 신맛이 매우 강함</t>
+          <t>매우 강한 신맛 — 신맛이 강하여 물과 함께 섭취해야 함</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2572,31 +2526,35 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 복용 후 혓바늘이 완화되고 피로감이 크게 줄어듦</t>
+          <t>확실한 효능 체감 — 피로감이 줄어들고 혓바늘 등 체력 회복에 효과적임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>올인원 영양 보충 — 액상과 정제가 함께 있어 한 포로 간단히 영양 보충</t>
+          <t>편리한 복합 구성 — 액상과 정제가 함께 들어 있어 한 번에 챙기기 좋음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>빠른 배송 및 할인 — 배송이 빠르고 할인 행사 시 가성비 높게 구매함</t>
+          <t>빠른 배송과 혜택 — 배송이 빠르고 이벤트 추가 증정 혜택이 만족스러움</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>아쉬운 유통기한 — 생각했던 것보다 유통기한 남아있는 기간이 짧음</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>짧은 유통기한 — 생각보다 유통기한이 짧아 아쉬움</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>가격 부담감 — 가격대가 높아 꾸준히 구매하기에는 다소 부담스러움</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2604,51 +2562,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>841</v>
+        <v>787</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 마신 후 피로가 완화되고 온종일 에너지가 유지됨</t>
+          <t>우수한 활력 증진 — 바쁜 일상 중 먹었을 때 활력이 생기고 피로가 개선됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>위생적인 2중 포장 — 액상과 알약이 분리되어 있어 깔끔하게 섭취 가능</t>
+          <t>쓰지 않은 목넘김 — 비타민 특유의 쓴맛이 없어 섭취하기 편함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 배송 — 배송이 빠르고 외출 시 휴대하며 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>선물용으로 유용 — 직장인 및 지인 선물용으로 만족도가 매우 높음</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 오렌지 맛 감기약 같은 향과 맛이 느껴짐</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -2694,18 +2656,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>다양한 맛과 식감 — 종류가 다양하여 다이어트 중 질리지 않고 부드러움</t>
+          <t>다양한 맛 구성 — 맛 종류가 많아 다이어트 중 질리지 않고 먹음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>간편한 조리 방법 — 전자레인지로 간단히 데워 한 끼를 떼우기 편함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>간편한 데우기 조리 — 전자레인지에 간단히 데워 한 끼를 해결할 수 있음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>부드러운 식감 — 살이 부드럽고 촉촉하여 맛있게 식단 관리를 함</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>초기 수량 누락 발생 — 배송 과정에서 일부 수량이 누락되는 일 발생함</t>
+          <t>배송 누락 발생 — 일부 수량이 누락되어 문의 후 재배송을 받음</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2753,20 +2719,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>속 편한 소화 도움 — 식후 소화가 잘 되고 편안한 상태가 유지됨</t>
+          <t>속 편한 소화 작용 — 식후 소화가 잘되고 속이 한결 편안해짐</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 패키지가 고급스러워 부담 없이 선물하기 적합함</t>
+          <t>고급스러운 포장 — 선물용 패키지가 깔끔하고 고급스러움</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>푸짐한 사은품 구성 — 견과류바 등 구성 사은품이 알차게 포함되어 제공됨</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>푸짐한 사은품 — 견과류바 등 구성 사은품이 알차고 만족스러움</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>기프티콘 확인 불편 — 증정 기프티콘 수령 위치 확인이 명확하지 않음</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -2812,28 +2782,32 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 포만감 — 맛있고 씹는 맛이 있어 한 개만으로도 포만감이 높음</t>
+          <t>높은 포만감 제공 — 한 개만 먹어도 포만감이 오래 유지됨</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>가성비와 예쁜 사은품 — 할인가로 저렴하게 구매 가능하며 보냉백 디자인이 예쁨</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>뛰어난 가성비 — 할인 가격에 구성이 알차고 사은품 가방이 예쁨</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>신속한 발송 — 배송 처리가 빠르고 안전함</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>구성품 오배송 발생 — 주문한 메뉴 대신 중복된 다른 제품이 배송되어 옴</t>
+          <t>구성품 오배송 — 주문 구성과 다르게 오배송되어 아쉬움</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>다소 강한 간 — 생각했던 것보다 제품의 간이 살짝 강함</t>
+          <t>약간 강한 간 — 단독 섭취 시 생각보다 간이 세게 느껴짐</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 배송 시 냉동 상태가 완벽하지 않고 약간 녹아 도착함</t>
+          <t>해동 상태 배송 — 배송 시 제품이 약간 녹아서 도착함</t>
         </is>
       </c>
     </row>
@@ -2875,22 +2849,26 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>장 건강 및 속 편함 — 복용 후 배에 가스가 차지 않고 변비가 완화됨</t>
+          <t>속 편한 소화 촉진 — 복용 후 변비와 배 가스 차는 현상이 완화됨</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>착한 가격과 풍성한 덤 — 저렴한 가격에 견과류바 등 푸짐한 덤이 제공됨</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>알찬 사은품 구성 — 저당견과류바 및 단백칩 등 증정품이 푸짐함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>먹기 편한 맛 — 맛이 좋아 거부감 없이 챙겨 먹기 적합함</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>아쉬운 냄새와 맛 — 기존 프리미엄 제품 대비 향과 맛이 떨어짐</t>
+          <t>호불호 있는 향과 맛 — 카무트 G 제품 특유의 냄새와 맛이 아쉬움</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2938,17 +2916,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>맛있는 효소 맛 — 거부감 없이 맛있게 간식처럼 먹기 좋음</t>
+          <t>맛있는 효소 제형 — 효소가 맛있어서 간식처럼 먹기 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>훌륭한 굿즈 퀄리티 — 동봉된 포토카드와 엽서의 디자인 및 퀄리티가 우수함</t>
+          <t>훌륭한 굿즈 퀄리티 — 포토카드와 엽서 디자인 및 품질이 뛰어남</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>빠르고 안전한 배송 — 배송이 빠르고 전체적인 구성 상품 만족도가 높음</t>
+          <t>빠른 배송 서비스 — 배송이 신속하고 안전하게 전달됨</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2997,17 +2975,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 맛 — 퍽퍽하지 않고 촉촉하며 소스 맛이 훌륭함</t>
+          <t>촉촉하고 맛있는 식감 — 퍽퍽하지 않고 촉촉하며 양념 맛이 우수함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>전자레인지 섭취 편의 — 전자레인지에 간편히 데워 바로 먹을 수 있음</t>
+          <t>간편한 레인지 조리 — 전자레인지로 데워 먹기 편해 간식/식사로 좋음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>질리지 않는 구성 — 다양한 맛으로구성되어 식단 관리에 용이함</t>
+          <t>합리적인 가격 — 저렴한 가격에 맛과 구성 만족도가 높음</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3017,7 +2995,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3025,48 +3003,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>64,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13255641</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021173253_c716df66353b42e9b0e73e5db0962008.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261022082137_8413f613a8ac4edb9b69847f419517ca.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>759</v>
+        <v>33</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 선물용 패키지가 예쁘고 고급스러워 만족도가 높음</t>
+          <t>달콤한 고구마맛 — 고구마맛이라 맛있어서 부담 없이 챙겨 먹음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>맛있는 앰플 제형 — 맛이 좋아 거부감 없이 하루 한 병씩 챙겨 먹기 편함</t>
+          <t>속 더부룩함 완화 — 식후 속 답답함과 더부룩함이 덜함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>피부 촉촉함 체감 — 꾸준한 섭취로 피부가 촉촉해지는 느낌을 받음</t>
+          <t>목 넘김 좋은 입자 — 분말이 고와 목에 걸리지 않고 양도 적당함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3111,21 +3089,21 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 다음 날 두통과 숙취가 확연히 줄어듦</t>
+          <t>확실한 숙취 해소 — 음주 전후 복용 시 다음 날 두통과 숙취가 적음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>간편한 스틱 액상 제형 — 물 없이 짜서 바로 먹을 수 있어 휴대와 섭취가 용이함</t>
+          <t>물 없는 액상 스틱 — 스틱 액상 형태라 휴대가 편하고 물 없이 먹음</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>고급 보라색 선물 박스 — 패키지가 깔끔하고 고급스러워 지인 선물용으로 적합</t>
+          <t>달달한 맛 — 거부감 없는 달콤한 맛으로 편하게 섭취함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3135,7 +3113,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3143,48 +3121,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13255641</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261022082137_8413f613a8ac4edb9b69847f419517ca.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021173253_c716df66353b42e9b0e73e5db0962008.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>759</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>맛있는 고구마맛 분말 — 인공적이지 않은 달콤한 고구마맛으로 맛있음</t>
+          <t>고급스러운 패키지 — 포장 디자인이 예쁘고 고급스러워 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>식후 속 더부룩함 감소 — 식후에 먹으면 더부룩한 속이 금방 편안해짐</t>
+          <t>맛있는 액상 제형 — 맛이 우수하여 하루 한 병씩 부담 없이 마심</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고운 입자와 스틱 포장 — 분말이 고와 목걸림이 없고 개별 포장이라 휴대성이 높음</t>
+          <t>피부 및 피로 케어 — 피부 탄력 증진과 피로 완화에 기대감을 줌</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3233,22 +3211,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 — 락토프리 제품으로 섭취 후 속이 편안함</t>
+          <t>비린 맛 없는 맛 — 단백질 특유의 비린 맛이 없고 맛있음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>맛있고 비린 맛 없음 — 단백질 특유의 비린 맛이 없고 일반 우유처럼 맛있음</t>
+          <t>속 편한 락토프리 — 락토프리 제품이라 마신 후 속이 편안함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>빠른 배송 및 증정품 — 배송이 빠르고 프로틴바 증정 구성이 만족스러움</t>
+          <t>간편한 식사 대용 — 아침이나 바쁠 때 간편하게 섭취하기 좋음</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>일부 맛의 느끼함 — 특정 맛의 경우 개인에 따라 다소 느끼하게 느껴짐</t>
+          <t>일부 맛의 느끼함 — 밀크바닐라 맛 등 특정 맛이 약간 느끼하게 느껴짐</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3410,7 +3388,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3445,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3502,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
     </row>
@@ -3575,10 +3553,10 @@
         <v>16325</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15665</v>
+        <v>15667</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6530</v>
@@ -3587,7 +3565,7 @@
         <v>829</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>8759</v>
@@ -3599,7 +3577,7 @@
         <v>130</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>841</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -3610,75 +3588,76 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 효과 체감 — 복용 후 컨디션 유지 및 피로 완화에 도움을 받음
-용이한 알약 섭취 — 알약 크기가 작고 맛이 강하지 않아 잘 넘어감
-선물용 높은 만족도 — 유명한 제품으로 선물 시 만족도가 뛰어남</t>
+          <t>피로 회복 효과 — 섭취 후 피곤함이 덜하고 컨디션 유지에 도움됨
+편리한 복용감 — 알약 크기가 작고 맛이 무난하여 복용하기 쉬움
+높은 선물 만족도 — 선물용으로 인기가 높으며 받았을 때 만족감이 큼</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 액상 섭취 — 액상이 달짝지근하고 신맛이 없어 맛있게 복용 가능함
-피로 회복 및 활력 — 복용 후 기운이 나고 피로 회복에 효과적임
-안전한 뽁뽁이 포장 — 에어캡 포장으로 손상 없이 완벽하게 배송됨</t>
+          <t>휴대성 및 깔끔 포장 — 포장이 깔끔하고 휴대하기 좋아 간편하게 챙겨 먹음
+달콤하고 맛있는 맛 — 액상이 달짝지근하고 시지 않아 맛있게 복용함
+기력 회복 도모 — 외출 전이나 지칠 때 기운을 차리는 데 도움됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>넉넉한 용량 구성 — 30+2입 구성으로 오래두고 챙겨 먹기 적합함
-진한 액상 농도 — 타 유사 액상 제품 대비 농도가 훨씬 찐함
-실용적인 선물용 — 생일이나 건강 기원 선물로 받는 만족도가 높음</t>
+          <t>진한 액상 농도 — 타 액상 비타민 제품 대비 농도가 찐함
+체력 충전 효과 — 지치고 체력이 달릴 때 먹으면 힘이 남
+알찬 선물 구성 — 30개입으로 용량이 넉넉하여 선물용으로 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 식감 — 과일맛이 나고 적당히 말랑하며 쫄깃해 맛있음
-간편한 씹어먹기 — 물 없이 씹어서 간 편하게 섭취 가능함
-안전 캡 포장 적용 — 안전캡이 적용되어 아이 있는 집에서도 안전함</t>
+          <t>맛있는 구미 제형 — 과일맛의 쫄깃한 젤리 형태로 간식처럼 섭취함
+물 없는 간편 섭취 — 바쁜 아침 물 없이 씹어 먹을 수 있어 편리함
+안전캡 적용 — 안전용기가 적용되어 아이가 있는 집에서도 보관 용이함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 일상생활 피로가 잘 풀리고 컨디션 회복에 도움 됨
-편리한 휴대성 — 휴대하기 편해 외출 시 간편히 챙겨 먹기 좋음
-만족스러운 선물 구성 — 기프트 에디션 구성이 좋아 선물용으로 매우 적합함</t>
+          <t>피로 회복 도움 — 피로 해소와 상쾌한 컨디션 유지에 효과적임
+간편한 휴대성 — 복용이 편하고 휴대하기 좋아 일상 활용도가 높음
+만족스러운 패키지 — 선물용 패키지 구성과 배송 만족도가 우수함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 포장용기와 패키지가 깔끔하고 고급스러움
-상큼한 맛과 에너지 — 상큼한 맛으로 에너지가 충전되는 느낌을 받음
-빠르고 꼼꼼한 배송 — 배송이 빠르고 꼼꼼하게 포장되어 전달됨</t>
+          <t>빠른 에너지 충전 — 달콤새콤한 맛으로 빠르게 기력이 나는 느낌임
+고급스러운 포장 — 패키지가 깔끔하고 고급스러워 응원 선물로 좋음
+간편한 복용법 — 깔끔하게 챙겨 먹기 유용하며 섭취가 편리함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 마시는 제형 — 액상 제형으로 물 없이 간편하게 섭취 가능함
-다음 날 피로 회복 — 섭취 후 다음 날 아침 컨디션 차이를 체감함
-센스 있는 선물용 — 체력 관리가 필요한 사람에게 선물하기 좋음</t>
+          <t>마시는 액상 제형 — 액상 형태로 섭취하기가 매우 간편함
+컨디션 회복 효과 — 피곤할 때 섭취하면 기운을 차리는 데 도움됨
+빠른 배송 서비스 — 배송이 빠르고 선물용으로 주고받기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송 및 가격 — 배송이 매우 빠르고 행사 가격으로 저렴하게 구입함
-믿을 수 있는 품질 — 영국산 퀄리씨 원료 사용으로 품질 신뢰도가 높음</t>
+          <t>신뢰도 높은 원료 — 영국산 퀄리씨 원료를 사용하여 믿고 구매함
+합리적인 가격 — 행사 및 할인가로 부담 없이 저렴하게 구매함
+메가도스에 적합 — 고용량 비타민C 메가도스 용법으로 챙기기 적합함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 복용 후 혓바늘이 완화되고 피로감이 크게 줄어듦
-올인원 영양 보충 — 액상과 정제가 함께 있어 한 포로 간단히 영양 보충
-빠른 배송 및 할인 — 배송이 빠르고 할인 행사 시 가성비 높게 구매함</t>
+          <t>확실한 효능 체감 — 피로감이 줄어들고 혓바늘 등 체력 회복에 효과적임
+편리한 복합 구성 — 액상과 정제가 함께 들어 있어 한 번에 챙기기 좋음
+빠른 배송과 혜택 — 배송이 빠르고 이벤트 추가 증정 혜택이 만족스러움</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 마신 후 피로가 완화되고 온종일 에너지가 유지됨
-위생적인 2중 포장 — 액상과 알약이 분리되어 있어 깔끔하게 섭취 가능
-간편한 휴대성과 배송 — 배송이 빠르고 외출 시 휴대하며 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>우수한 활력 증진 — 바쁜 일상 중 먹었을 때 활력이 생기고 피로가 개선됨
+쓰지 않은 목넘김 — 비타민 특유의 쓴맛이 없어 섭취하기 편함
+선물용으로 유용 — 직장인 및 지인 선물용으로 만족도가 매우 높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3686,34 +3665,39 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>높은 가격 부담 — 제품 가격이 비싸 구매 시 부담이 큼</t>
+          <t>부담스러운 가격 — 가격대가 비싸 할인 기간을 활용하여 구매함</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>개봉 시 씰링 불편 — 개봉 시 비닐 포장이 잘 안 뜯겨 불편함</t>
+          <t>개봉의 어려움 — 포장이 잘 뜯기지 않아 개봉 시 다소 불편함</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>생소한 복용 방식 — 뚜껑을 눌러 섞어 마시는 방식이 처음엔 다소 어색함</t>
+          <t>복용 방식의 생소함 — 뚜껑을 눌러 섞어 마시는 형태라 복용법 확인이 필요함</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>매우 강한 신맛 — 정신이 번쩍 들 정도로 분말의 신맛이 매우 강함</t>
+          <t>매우 강한 신맛 — 신맛이 강하여 물과 함께 섭취해야 함</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 유통기한 — 생각했던 것보다 유통기한 남아있는 기간이 짧음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>짧은 유통기한 — 생각보다 유통기한이 짧아 아쉬움
+가격 부담감 — 가격대가 높아 꾸준히 구매하기에는 다소 부담스러움</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 오렌지 맛 감기약 같은 향과 맛이 느껴짐</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -3768,7 +3752,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3925,17 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -3998,17 +3982,17 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4055,17 +4039,17 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4127,7 +4111,7 @@
         <v>159</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>270</v>
@@ -4136,13 +4120,13 @@
         <v>70</v>
       </c>
       <c r="I19" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="K19" s="3" t="n">
         <v>759</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>33</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>31</v>
@@ -4156,69 +4140,72 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛과 식감 — 종류가 다양하여 다이어트 중 질리지 않고 부드러움
-간편한 조리 방법 — 전자레인지로 간단히 데워 한 끼를 떼우기 편함</t>
+          <t>다양한 맛 구성 — 맛 종류가 많아 다이어트 중 질리지 않고 먹음
+간편한 데우기 조리 — 전자레인지에 간단히 데워 한 끼를 해결할 수 있음
+부드러운 식감 — 살이 부드럽고 촉촉하여 맛있게 식단 관리를 함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 도움 — 식후 소화가 잘 되고 편안한 상태가 유지됨
-고급스러운 선물 포장 — 패키지가 고급스러워 부담 없이 선물하기 적합함
-푸짐한 사은품 구성 — 견과류바 등 구성 사은품이 알차게 포함되어 제공됨</t>
+          <t>속 편한 소화 작용 — 식후 소화가 잘되고 속이 한결 편안해짐
+고급스러운 포장 — 선물용 패키지가 깔끔하고 고급스러움
+푸짐한 사은품 — 견과류바 등 구성 사은품이 알차고 만족스러움</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 포만감 — 맛있고 씹는 맛이 있어 한 개만으로도 포만감이 높음
-가성비와 예쁜 사은품 — 할인가로 저렴하게 구매 가능하며 보냉백 디자인이 예쁨</t>
+          <t>높은 포만감 제공 — 한 개만 먹어도 포만감이 오래 유지됨
+뛰어난 가성비 — 할인 가격에 구성이 알차고 사은품 가방이 예쁨
+신속한 발송 — 배송 처리가 빠르고 안전함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>장 건강 및 속 편함 — 복용 후 배에 가스가 차지 않고 변비가 완화됨
-착한 가격과 풍성한 덤 — 저렴한 가격에 견과류바 등 푸짐한 덤이 제공됨</t>
+          <t>속 편한 소화 촉진 — 복용 후 변비와 배 가스 차는 현상이 완화됨
+알찬 사은품 구성 — 저당견과류바 및 단백칩 등 증정품이 푸짐함
+먹기 편한 맛 — 맛이 좋아 거부감 없이 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 효소 맛 — 거부감 없이 맛있게 간식처럼 먹기 좋음
-훌륭한 굿즈 퀄리티 — 동봉된 포토카드와 엽서의 디자인 및 퀄리티가 우수함
-빠르고 안전한 배송 — 배송이 빠르고 전체적인 구성 상품 만족도가 높음</t>
+          <t>맛있는 효소 제형 — 효소가 맛있어서 간식처럼 먹기 좋음
+훌륭한 굿즈 퀄리티 — 포토카드와 엽서 디자인 및 품질이 뛰어남
+빠른 배송 서비스 — 배송이 신속하고 안전하게 전달됨</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 맛 — 퍽퍽하지 않고 촉촉하며 소스 맛이 훌륭함
-전자레인지 섭취 편의 — 전자레인지에 간편히 데워 바로 먹을 수 있음
-질리지 않는 구성 — 다양한 맛으로구성되어 식단 관리에 용이함</t>
+          <t>촉촉하고 맛있는 식감 — 퍽퍽하지 않고 촉촉하며 양념 맛이 우수함
+간편한 레인지 조리 — 전자레인지로 데워 먹기 편해 간식/식사로 좋음
+합리적인 가격 — 저렴한 가격에 맛과 구성 만족도가 높음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 선물용 패키지가 예쁘고 고급스러워 만족도가 높음
-맛있는 앰플 제형 — 맛이 좋아 거부감 없이 하루 한 병씩 챙겨 먹기 편함
-피부 촉촉함 체감 — 꾸준한 섭취로 피부가 촉촉해지는 느낌을 받음</t>
+          <t>달콤한 고구마맛 — 고구마맛이라 맛있어서 부담 없이 챙겨 먹음
+속 더부룩함 완화 — 식후 속 답답함과 더부룩함이 덜함
+목 넘김 좋은 입자 — 분말이 고와 목에 걸리지 않고 양도 적당함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 다음 날 두통과 숙취가 확연히 줄어듦
-간편한 스틱 액상 제형 — 물 없이 짜서 바로 먹을 수 있어 휴대와 섭취가 용이함
-고급 보라색 선물 박스 — 패키지가 깔끔하고 고급스러워 지인 선물용으로 적합</t>
+          <t>확실한 숙취 해소 — 음주 전후 복용 시 다음 날 두통과 숙취가 적음
+물 없는 액상 스틱 — 스틱 액상 형태라 휴대가 편하고 물 없이 먹음
+달달한 맛 — 거부감 없는 달콤한 맛으로 편하게 섭취함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 고구마맛 분말 — 인공적이지 않은 달콤한 고구마맛으로 맛있음
-식후 속 더부룩함 감소 — 식후에 먹으면 더부룩한 속이 금방 편안해짐
-고운 입자와 스틱 포장 — 분말이 고와 목걸림이 없고 개별 포장이라 휴대성이 높음</t>
+          <t>고급스러운 패키지 — 포장 디자인이 예쁘고 고급스러워 선물용으로 훌륭함
+맛있는 액상 제형 — 맛이 우수하여 하루 한 병씩 부담 없이 마심
+피부 및 피로 케어 — 피부 탄력 증진과 피로 완화에 기대감을 줌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 — 락토프리 제품으로 섭취 후 속이 편안함
-맛있고 비린 맛 없음 — 단백질 특유의 비린 맛이 없고 일반 우유처럼 맛있음
-빠른 배송 및 증정품 — 배송이 빠르고 프로틴바 증정 구성이 만족스러움</t>
+          <t>비린 맛 없는 맛 — 단백질 특유의 비린 맛이 없고 맛있음
+속 편한 락토프리 — 락토프리 제품이라 마신 후 속이 편안함
+간편한 식사 대용 — 아침이나 바쁠 때 간편하게 섭취하기 좋음</t>
         </is>
       </c>
     </row>
@@ -4230,20 +4217,24 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>초기 수량 누락 발생 — 배송 과정에서 일부 수량이 누락되는 일 발생함</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
+          <t>배송 누락 발생 — 일부 수량이 누락되어 문의 후 재배송을 받음</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>기프티콘 확인 불편 — 증정 기프티콘 수령 위치 확인이 명확하지 않음</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>구성품 오배송 발생 — 주문한 메뉴 대신 중복된 다른 제품이 배송되어 옴
-다소 강한 간 — 생각했던 것보다 제품의 간이 살짝 강함
-배송 중 해동 상태 — 배송 시 냉동 상태가 완벽하지 않고 약간 녹아 도착함</t>
+          <t>구성품 오배송 — 주문 구성과 다르게 오배송되어 아쉬움
+약간 강한 간 — 단독 섭취 시 생각보다 간이 세게 느껴짐
+해동 상태 배송 — 배송 시 제품이 약간 녹아서 도착함</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 냄새와 맛 — 기존 프리미엄 제품 대비 향과 맛이 떨어짐</t>
+          <t>호불호 있는 향과 맛 — 카무트 G 제품 특유의 냄새와 맛이 아쉬움</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -4253,7 +4244,7 @@
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>일부 맛의 느끼함 — 특정 맛의 경우 개인에 따라 다소 느끼하게 느껴짐</t>
+          <t>일부 맛의 느끼함 — 밀크바닐라 맛 등 특정 맛이 약간 느끼하게 느껴짐</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4286,17 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t>64,900원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>65,900원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>64,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4508,14 +4499,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
+          <t>베러핏 고단백 저당쉐이크 흑임자맛</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>1,000원</t>
@@ -4523,39 +4510,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
-        </is>
-      </c>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031386198&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>737</v>
+        <v>972</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤하고 맛있어서 입 심심할 때 간식처럼 먹기 좋음</t>
+          <t>우수한 가성비 — 가격 대비 영양 성분이 양호함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>우수한 가성비 및 효과 — 가격 대비 배변 보조 및 소화 효과가 훌륭함</t>
+          <t>고소하고 잘 녹는 제형 — 두유나 물에 잘 녹으며 고소함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 맛이 입에 맞지 않거나 지나치게 달게 느껴짐</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4563,12 +4550,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4578,32 +4565,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>196</v>
+        <v>7057</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 붓기 관리 캔디 — 붓기 관리용으로 맛나게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>아쉬운 맛과 효능 체감 — 효과를 체감하기 어렵고 다소 애매한 알약 맛이 남</t>
-        </is>
-      </c>
+          <t>압도적 가성비 — 가격 부담이 적어 지속 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>근육 떨림 완화 — 복용 후 근육 떨림 증상이 줄어듦</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>빠른 배송 서비스 — 택배 배송이 빠르게 도착함</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -4618,58 +4609,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306209&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/rS9JgHwoY8ffaFGoRZTx032306209_00_01rS9JgHwoY8ffaFGoRZTx.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>416</v>
+        <v>2684</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>건강 챙기는 구미 간식 — 간식처럼 먹으면서 건강을 챙길 수 있음</t>
+          <t>우수한 가성비 — 가격 대비 만족도가 높음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>수면 도움 활용 — 밤에 취침 전 섭취 시 숙면에 무난히 도움이 됨</t>
+          <t>비타민C와 섭취 적합 — 비타민C와 함께 섭취하여 건강 관리에 활용함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>간식 대비 높은 가격 — 기능 체감이 크지 않고 단순 간식용으로는 비싼 편임</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4677,46 +4664,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000283&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/zIbSOpTi3yHSeYULrLdY600000283_00_01zIbSOpTi3yHSeYULrLdY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>295</v>
+        <v>778</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>높은 가성비 만족 — 저렴한 가격에 다이소에서 부담 없이 구매 가능함</t>
+          <t>착한 가격대 — 저렴한 가격에 홍삼을 구매할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>우수한 개인 체질 적합성 — 기존 복용해 본 비타민 중 가장 몸에 잘 맞음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>진한 향과 맛 — 사포닌 향이 나고 맛이 진함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>간절기 건강 관리 — 간절기에 한 포씩 챙겨 먹기 유용함</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -4724,7 +4715,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4732,62 +4723,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678604&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/GVr6GsoojIJO6UtcBMHG601678604_00_02GVr6GsoojIJO6UtcBMHG.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1604</v>
+        <v>120</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>저렴한 가격의 영양제 — 부담 없는 저렴한 가격으로 30일분을 챙길 수 있음</t>
+          <t>상큼하고 맛있는 맛 — 레몬맛이라 상큼하여 사탕처럼 먹기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 섭취 용량 — 한 달치 분량으로 하루 정량을 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>미미한 효과 체감 — 장기간 복용해도 뚜렷한 효과를 느끼기 힘듦</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>과도한 패키지 포장 — 내용물 양에 비해 패키지 포장이 과한 느낌임</t>
-        </is>
-      </c>
+          <t>뛰어난 가성비 — 가격이 싸고 품질 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>휴대 및 간식용 적합 — 크기가 적당해 들고 다니며 졸릴 때 섭취함</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4795,12 +4782,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4810,28 +4797,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1166</v>
+        <v>7542</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 필요한 만큼 소량 구매할 수 있고 가성비가 훌륭함</t>
+          <t>높은 가성비 — 저렴한 가격으로 코큐텐을 복용할 수 있음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 기운 충전 — 기운이 없거나 감기 기운이 있을 때 간편히 섭취함</t>
+          <t>만족스러운 함량 — 국내 제품 기준 함량이 우수함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -4842,7 +4829,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4850,12 +4837,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4865,36 +4852,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602146&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260922/duhAbxLjwmJEME9SWJfp613602146_00_01duhAbxLjwmJEME9SWJfp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>693</v>
+        <v>6847</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 대체 영양제 — 피곤할 때나 여행 중 간편하게 비타민 챙기기 좋음</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>저렴한 구매 가격 — 가격이 싸서 부담 없이 활력 영양제로 복용 가능함</t>
+          <t>양호한 성분 구성 — 약사 추천 등 성분이 양호하여 만족함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>호불호 있는 독특한 맛 — 맛이 다소 아리까리하고 명확하지 않음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -4909,49 +4892,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] [인교진 PICK] 기억력 건강 올인원 15포 15일분</t>
+          <t>[에너지] 동화약품 배러크런치B 오렌지맛 30정 10일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991017&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678603&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260928/S7HdATle74UMTysUx3Dz033991017_00_00S7HdATle74UMTysUx3Dz.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/1iaDXDZs14qWRuWOkuNr601678603_00_021iaDXDZs14qWRuWOkuNr.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>부담 없는 높은 가성비 — 가격이 저렴해 부담 없이 구매하기 좋음</t>
+          <t>저렴한 가격 — 부담 없이 간식 겸용 영양제로 구매함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>심리적 안심 및 편의성 — 먹기에 부담이 없고 챙겨 먹으면 마음이 안심됨</t>
+          <t>졸음 방지용 섭취 — 운전 중이나 졸릴 때 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>미미한 체감 효능 — 기억력 개선 등의 효과가 미미하여 즉각적인 체감이 어려움</t>
+          <t>씁쓸한 끝맛과 적은 양 — 끝맛에 쓴맛이 나며 양이 다소 적게 느껴짐</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -4960,7 +4943,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4968,49 +4951,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>6845</v>
+        <v>2956</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>만족스러운 높은 가성비 — 가격 부담이 적고 품질에 만족하여 재구매함</t>
+          <t>카페인 적은 커피 대용 — 카페인 부담 없이 커피 대용으로 마심</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>피부 상태 개선 도움 — 꾸준히 복용 후 피부 상태가 좋아지는 데 도움 됨</t>
+          <t>배변 활동에 도움 — 섭취 후 화장실을 원활하게 가는 데 도움됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>불명확한 단기 효과 — 단기 복용으로는 뚜렷한 효과를 바로 확인하기 어려움</t>
+          <t>씁쓸한 향과 맛 — 아메리카노 향과 함께 약간 쓴맛이 감돎</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5019,7 +5002,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5027,12 +5010,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5042,36 +5025,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>7533</v>
+        <v>863</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>착한 가격과 좋은 함량 — 국내 제품 중 착한 가격과 알찬 함량을 갖춤</t>
+          <t>가성비 및 체감 효과 — 가격이 저렴하고 운동 시 체감이 느껴짐</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>편리한 소분 포장 — 소포장되어 있어 개별 보관 및 섭취하기가 편함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>혈압 건강 관리 목적 — 혈압 및 일상 건강 관리를 위해 지속 복용하기 좋음</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>운동 후 회복 도움 — 운동 다음 날 몸이 편안함을 느낌</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>아쉬운 함량과 용량 — 용량이 작고 함량이 다소 낮다고 느껴짐</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5191,47 +5174,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5241,54 +5224,50 @@
           <t>브랜드</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -5300,52 +5279,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>베러핏 고단백 저당쉐이크 흑임자맛</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>[항산화] 동화약품 배러크런치C 레몬맛 30정 10일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] [인교진 PICK] 기억력 건강 올인원 15포 15일분</t>
+          <t>[에너지] 동화약품 배러크런치B 오렌지맛 30정 10일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
     </row>
@@ -5356,10 +5335,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5368,7 +5347,7 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5377,10 +5356,10 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5393,34 +5372,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>737</v>
+        <v>972</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>196</v>
+        <v>7057</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>416</v>
+        <v>2684</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>295</v>
+        <v>778</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1604</v>
+        <v>120</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1166</v>
+        <v>7542</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>693</v>
+        <v>6847</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>6845</v>
+        <v>2956</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>7533</v>
+        <v>863</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5431,106 +5410,100 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤하고 맛있어서 입 심심할 때 간식처럼 먹기 좋음
-우수한 가성비 및 효과 — 가격 대비 배변 보조 및 소화 효과가 훌륭함</t>
+          <t>우수한 가성비 — 가격 대비 영양 성분이 양호함
+고소하고 잘 녹는 제형 — 두유나 물에 잘 녹으며 고소함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 붓기 관리 캔디 — 붓기 관리용으로 맛나게 먹을 수 있음</t>
+          <t>압도적 가성비 — 가격 부담이 적어 지속 복용하기 좋음
+근육 떨림 완화 — 복용 후 근육 떨림 증상이 줄어듦
+빠른 배송 서비스 — 택배 배송이 빠르게 도착함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>건강 챙기는 구미 간식 — 간식처럼 먹으면서 건강을 챙길 수 있음
-수면 도움 활용 — 밤에 취침 전 섭취 시 숙면에 무난히 도움이 됨</t>
+          <t>우수한 가성비 — 가격 대비 만족도가 높음
+비타민C와 섭취 적합 — 비타민C와 함께 섭취하여 건강 관리에 활용함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>높은 가성비 만족 — 저렴한 가격에 다이소에서 부담 없이 구매 가능함
-우수한 개인 체질 적합성 — 기존 복용해 본 비타민 중 가장 몸에 잘 맞음</t>
+          <t>착한 가격대 — 저렴한 가격에 홍삼을 구매할 수 있음
+진한 향과 맛 — 사포닌 향이 나고 맛이 진함
+간절기 건강 관리 — 간절기에 한 포씩 챙겨 먹기 유용함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격의 영양제 — 부담 없는 저렴한 가격으로 30일분을 챙길 수 있음
-간편한 섭취 용량 — 한 달치 분량으로 하루 정량을 챙겨 먹기 편함</t>
+          <t>상큼하고 맛있는 맛 — 레몬맛이라 상큼하여 사탕처럼 먹기 좋음
+뛰어난 가성비 — 가격이 싸고 품질 만족도가 높음
+휴대 및 간식용 적합 — 크기가 적당해 들고 다니며 졸릴 때 섭취함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 필요한 만큼 소량 구매할 수 있고 가성비가 훌륭함
-간편한 기운 충전 — 기운이 없거나 감기 기운이 있을 때 간편히 섭취함</t>
+          <t>높은 가성비 — 저렴한 가격으로 코큐텐을 복용할 수 있음
+만족스러운 함량 — 국내 제품 기준 함량이 우수함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 대체 영양제 — 피곤할 때나 여행 중 간편하게 비타민 챙기기 좋음
-저렴한 구매 가격 — 가격이 싸서 부담 없이 활력 영양제로 복용 가능함</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 챙겨 먹기 좋음
+양호한 성분 구성 — 약사 추천 등 성분이 양호하여 만족함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 높은 가성비 — 가격이 저렴해 부담 없이 구매하기 좋음
-심리적 안심 및 편의성 — 먹기에 부담이 없고 챙겨 먹으면 마음이 안심됨</t>
+          <t>저렴한 가격 — 부담 없이 간식 겸용 영양제로 구매함
+졸음 방지용 섭취 — 운전 중이나 졸릴 때 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>만족스러운 높은 가성비 — 가격 부담이 적고 품질에 만족하여 재구매함
-피부 상태 개선 도움 — 꾸준히 복용 후 피부 상태가 좋아지는 데 도움 됨</t>
+          <t>카페인 적은 커피 대용 — 카페인 부담 없이 커피 대용으로 마심
+배변 활동에 도움 — 섭취 후 화장실을 원활하게 가는 데 도움됨</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격과 좋은 함량 — 국내 제품 중 착한 가격과 알찬 함량을 갖춤
-편리한 소분 포장 — 소포장되어 있어 개별 보관 및 섭취하기가 편함
-혈압 건강 관리 목적 — 혈압 및 일상 건강 관리를 위해 지속 복용하기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>가성비 및 체감 효과 — 가격이 저렴하고 운동 시 체감이 느껴짐
+운동 후 회복 도움 — 운동 다음 날 몸이 편안함을 느낌</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>아쉬운 맛과 효능 체감 — 효과를 체감하기 어렵고 다소 애매한 알약 맛이 남</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>간식 대비 높은 가격 — 기능 체감이 크지 않고 단순 간식용으로는 비싼 편임</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 맛이 입에 맞지 않거나 지나치게 달게 느껴짐</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>미미한 효과 체감 — 장기간 복용해도 뚜렷한 효과를 느끼기 힘듦
-과도한 패키지 포장 — 내용물 양에 비해 패키지 포장이 과한 느낌임</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>호불호 있는 독특한 맛 — 맛이 다소 아리까리하고 명확하지 않음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>미미한 체감 효능 — 기억력 개선 등의 효과가 미미하여 즉각적인 체감이 어려움</t>
+          <t>씁쓸한 끝맛과 적은 양 — 끝맛에 쓴맛이 나며 양이 다소 적게 느껴짐</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>불명확한 단기 효과 — 단기 복용으로는 뚜렷한 효과를 바로 확인하기 어려움</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>씁쓸한 향과 맛 — 아메리카노 향과 함께 약간 쓴맛이 감돎</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 함량과 용량 — 용량이 작고 함량이 다소 낮다고 느껴짐</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5550,37 +5523,37 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5673,7 +5646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5710,16 +5683,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>36.7</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5729,16 +5702,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>23.3</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5748,22 +5721,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5782,20 +5755,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5839,7 +5812,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5852,6 +5825,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
     </row>
